--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_transfer_point.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_transfer_point.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="18585" windowHeight="11175"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_transfer_point" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="297">
   <si>
     <t>编号id</t>
   </si>
@@ -224,7 +224,7 @@
     <t>1031</t>
   </si>
   <si>
-    <t>罗兰峡谷</t>
+    <t>Loren Castle Siege</t>
   </si>
   <si>
     <t>从罗兰峡谷到罗兰峡谷</t>
@@ -263,7 +263,7 @@
     <t>1004</t>
   </si>
   <si>
-    <t>勇者大陆</t>
+    <t>Lorencia</t>
   </si>
   <si>
     <t>从仙踪林到勇者大陆</t>
@@ -537,7 +537,7 @@
     <t>1034</t>
   </si>
   <si>
-    <t>仙踪林</t>
+    <t>Noria</t>
   </si>
   <si>
     <t>从幽暗森林到仙踪林</t>
@@ -617,7 +617,7 @@
     <t>1052</t>
   </si>
   <si>
-    <t>冰风谷</t>
+    <t>Devias</t>
   </si>
   <si>
     <t>从幻术园到冰风谷</t>
@@ -668,7 +668,7 @@
     <t>1038</t>
   </si>
   <si>
-    <t>死亡沙漠</t>
+    <t>Desert</t>
   </si>
   <si>
     <t>从坎特鲁废墟到死亡沙漠</t>
@@ -730,7 +730,7 @@
     <t>100403</t>
   </si>
   <si>
-    <t>幽暗森林</t>
+    <t>Swamp of Calmness</t>
   </si>
   <si>
     <t>从仙踪林到幽暗森林</t>
@@ -751,7 +751,7 @@
     <t>1039</t>
   </si>
   <si>
-    <t>坎特鲁废墟</t>
+    <t>Kanturu Ruins</t>
   </si>
   <si>
     <t>从坎特鲁遗址到坎特鲁废墟</t>
@@ -787,7 +787,7 @@
     <t>103802</t>
   </si>
   <si>
-    <t>坎特鲁遗址</t>
+    <t>Kanturu Remain</t>
   </si>
   <si>
     <t>从坎特鲁废墟到坎特鲁遗址</t>
@@ -808,7 +808,7 @@
     <t>100206</t>
   </si>
   <si>
-    <t>地下城3</t>
+    <t>Dungeon 3</t>
   </si>
   <si>
     <r>
@@ -857,13 +857,25 @@
     <t>100204</t>
   </si>
   <si>
+    <t>2#17</t>
+  </si>
+  <si>
+    <t>7#85</t>
+  </si>
+  <si>
+    <t>100203</t>
+  </si>
+  <si>
+    <t>Dungeon 1</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>地下城</t>
+      <t>从地下城</t>
     </r>
     <r>
       <rPr>
@@ -871,26 +883,386 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>232#128</t>
+  </si>
+  <si>
+    <t>243#149</t>
+  </si>
+  <si>
+    <t>100202</t>
+  </si>
+  <si>
+    <t>Dungeon 2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到地下城2</t>
+    </r>
+  </si>
+  <si>
+    <t>239#149</t>
+  </si>
+  <si>
+    <t>233#123</t>
+  </si>
+  <si>
+    <t>100101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dungeon </t>
+  </si>
+  <si>
+    <t>从勇者大陆到地下城</t>
+  </si>
+  <si>
+    <t>122#232</t>
+  </si>
+  <si>
+    <t>0.5#0.5#-2</t>
+  </si>
+  <si>
+    <t>110#245</t>
+  </si>
+  <si>
+    <t>从地下城3到地下城2</t>
+  </si>
+  <si>
+    <t>2#85</t>
+  </si>
+  <si>
+    <t>0#0.5#-1</t>
+  </si>
+  <si>
+    <t>7#18</t>
+  </si>
+  <si>
+    <t>29#127</t>
+  </si>
+  <si>
+    <t>1#0.5#-2.5</t>
+  </si>
+  <si>
+    <t>8#28</t>
+  </si>
+  <si>
+    <t>100304</t>
+  </si>
+  <si>
+    <t>Ice Castle</t>
+  </si>
+  <si>
+    <t>从冰风谷到冰霜之城</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=330</t>
+  </si>
+  <si>
+    <t>53#92</t>
+  </si>
+  <si>
+    <t>1058</t>
+  </si>
+  <si>
+    <t>224#209</t>
+  </si>
+  <si>
+    <t>105708</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>Aida</t>
+  </si>
+  <si>
+    <t>从安宁池上岛到安宁池左上</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=350</t>
+  </si>
+  <si>
+    <t>57#176</t>
+  </si>
+  <si>
+    <t>138#109</t>
+  </si>
+  <si>
+    <t>105707</t>
+  </si>
+  <si>
+    <t>从安宁池左上到安宁池上岛</t>
+  </si>
+  <si>
+    <t>124#109</t>
+  </si>
+  <si>
+    <t>64#177</t>
+  </si>
+  <si>
+    <t>105706</t>
+  </si>
+  <si>
+    <t>从安宁池左岛到安宁池左上</t>
+  </si>
+  <si>
+    <t>68#52</t>
+  </si>
+  <si>
+    <t>2#1#0</t>
+  </si>
+  <si>
+    <t>0#-120#0</t>
+  </si>
+  <si>
+    <t>105705</t>
+  </si>
+  <si>
+    <t>从安宁池左下到安宁池左岛</t>
+  </si>
+  <si>
+    <t>139#95</t>
+  </si>
+  <si>
+    <t>2#0.5#-1.5</t>
+  </si>
+  <si>
+    <t>66#46</t>
+  </si>
+  <si>
+    <t>105704</t>
+  </si>
+  <si>
+    <t>从安宁池下岛到安宁池右下</t>
+  </si>
+  <si>
+    <t>197#13</t>
+  </si>
+  <si>
+    <t>105703</t>
+  </si>
+  <si>
+    <t>从安宁池右下到安宁池下岛</t>
+  </si>
+  <si>
+    <t>149#109</t>
+  </si>
+  <si>
+    <t>204#12</t>
+  </si>
+  <si>
+    <t>105702</t>
+  </si>
+  <si>
+    <t>从安宁池右岛到安宁池右上</t>
+  </si>
+  <si>
+    <t>185#187</t>
+  </si>
+  <si>
+    <t>0#60#0</t>
+  </si>
+  <si>
+    <t>105701</t>
+  </si>
+  <si>
+    <t>从安宁池右上到安宁池右岛</t>
+  </si>
+  <si>
+    <t>139#125</t>
+  </si>
+  <si>
+    <t>0#180#0</t>
+  </si>
+  <si>
+    <t>191#191</t>
+  </si>
+  <si>
+    <t>黄金安宁池</t>
+  </si>
+  <si>
+    <t>从黄金安宁池到黄金安宁池</t>
+  </si>
+  <si>
+    <t>100506</t>
+  </si>
+  <si>
+    <t>Lost Tower 7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <t>checkLevel&gt;=40</t>
+  </si>
+  <si>
+    <t>6#6</t>
+  </si>
+  <si>
+    <t>9#87</t>
+  </si>
+  <si>
+    <t>100505</t>
+  </si>
+  <si>
+    <t>Lost Tower 6</t>
+  </si>
+  <si>
+    <t>从失落之塔5到失落之塔6</t>
+  </si>
+  <si>
+    <t>131#16</t>
+  </si>
+  <si>
+    <t>54#55</t>
+  </si>
+  <si>
+    <t>100504</t>
+  </si>
+  <si>
+    <t>Lost Tower 5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <t>133#135</t>
+  </si>
+  <si>
+    <t>131#51</t>
+  </si>
+  <si>
+    <t>100503</t>
+  </si>
+  <si>
+    <t>Lost Tower 4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>3</t>
     </r>
-  </si>
-  <si>
-    <t>2#17</t>
-  </si>
-  <si>
-    <t>7#85</t>
-  </si>
-  <si>
-    <t>100203</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>地下城</t>
+      <t>到失落之塔</t>
     </r>
     <r>
       <rPr>
@@ -898,8 +1270,20 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>1</t>
-    </r>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <t>133#245</t>
+  </si>
+  <si>
+    <t>87#90</t>
+  </si>
+  <si>
+    <t>100502</t>
+  </si>
+  <si>
+    <t>Lost Tower 3</t>
   </si>
   <si>
     <r>
@@ -908,7 +1292,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>从地下城</t>
+      <t>从失落之塔</t>
     </r>
     <r>
       <rPr>
@@ -924,7 +1308,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>到地下城</t>
+      <t>到失落之塔</t>
     </r>
     <r>
       <rPr>
@@ -932,521 +1316,8 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>232#128</t>
-  </si>
-  <si>
-    <t>243#149</t>
-  </si>
-  <si>
-    <t>100202</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>地下城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从地下城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到地下城2</t>
-    </r>
-  </si>
-  <si>
-    <t>239#149</t>
-  </si>
-  <si>
-    <t>233#123</t>
-  </si>
-  <si>
-    <t>100101</t>
-  </si>
-  <si>
-    <t>地下城</t>
-  </si>
-  <si>
-    <t>从勇者大陆到地下城</t>
-  </si>
-  <si>
-    <t>122#232</t>
-  </si>
-  <si>
-    <t>0.5#0.5#-2</t>
-  </si>
-  <si>
-    <t>110#245</t>
-  </si>
-  <si>
-    <t>地下城2</t>
-  </si>
-  <si>
-    <t>从地下城3到地下城2</t>
-  </si>
-  <si>
-    <t>2#85</t>
-  </si>
-  <si>
-    <t>0#0.5#-1</t>
-  </si>
-  <si>
-    <t>7#18</t>
-  </si>
-  <si>
-    <t>29#127</t>
-  </si>
-  <si>
-    <t>1#0.5#-2.5</t>
-  </si>
-  <si>
-    <t>8#28</t>
-  </si>
-  <si>
-    <t>100304</t>
-  </si>
-  <si>
-    <t>冰霜之城</t>
-  </si>
-  <si>
-    <t>从冰风谷到冰霜之城</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=330</t>
-  </si>
-  <si>
-    <t>53#92</t>
-  </si>
-  <si>
-    <t>1058</t>
-  </si>
-  <si>
-    <t>224#209</t>
-  </si>
-  <si>
-    <t>105708</t>
-  </si>
-  <si>
-    <t>1057</t>
-  </si>
-  <si>
-    <t>安宁池</t>
-  </si>
-  <si>
-    <t>从安宁池上岛到安宁池左上</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=370</t>
-  </si>
-  <si>
-    <t>57#176</t>
-  </si>
-  <si>
-    <t>138#109</t>
-  </si>
-  <si>
-    <t>105707</t>
-  </si>
-  <si>
-    <t>从安宁池左上到安宁池上岛</t>
-  </si>
-  <si>
-    <t>124#109</t>
-  </si>
-  <si>
-    <t>64#177</t>
-  </si>
-  <si>
-    <t>105706</t>
-  </si>
-  <si>
-    <t>从安宁池左岛到安宁池左上</t>
-  </si>
-  <si>
-    <t>68#52</t>
-  </si>
-  <si>
-    <t>2#1#0</t>
-  </si>
-  <si>
-    <t>0#-120#0</t>
-  </si>
-  <si>
-    <t>105705</t>
-  </si>
-  <si>
-    <t>从安宁池左下到安宁池左岛</t>
-  </si>
-  <si>
-    <t>139#95</t>
-  </si>
-  <si>
-    <t>2#0.5#-1.5</t>
-  </si>
-  <si>
-    <t>66#46</t>
-  </si>
-  <si>
-    <t>105704</t>
-  </si>
-  <si>
-    <t>从安宁池下岛到安宁池右下</t>
-  </si>
-  <si>
-    <t>197#13</t>
-  </si>
-  <si>
-    <t>105703</t>
-  </si>
-  <si>
-    <t>从安宁池右下到安宁池下岛</t>
-  </si>
-  <si>
-    <t>149#109</t>
-  </si>
-  <si>
-    <t>204#12</t>
-  </si>
-  <si>
-    <t>105702</t>
-  </si>
-  <si>
-    <t>从安宁池右岛到安宁池右上</t>
-  </si>
-  <si>
-    <t>185#187</t>
-  </si>
-  <si>
-    <t>0#60#0</t>
-  </si>
-  <si>
-    <t>105701</t>
-  </si>
-  <si>
-    <t>从安宁池右上到安宁池右岛</t>
-  </si>
-  <si>
-    <t>139#125</t>
-  </si>
-  <si>
-    <t>0#180#0</t>
-  </si>
-  <si>
-    <t>191#191</t>
-  </si>
-  <si>
-    <t>黄金安宁池</t>
-  </si>
-  <si>
-    <t>从黄金安宁池到黄金安宁池</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=350</t>
-  </si>
-  <si>
-    <t>100506</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
-    <t>checkLevel&gt;=40</t>
-  </si>
-  <si>
-    <t>6#6</t>
-  </si>
-  <si>
-    <t>9#87</t>
-  </si>
-  <si>
-    <t>100505</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-  </si>
-  <si>
-    <t>从失落之塔5到失落之塔6</t>
-  </si>
-  <si>
-    <t>131#16</t>
-  </si>
-  <si>
-    <t>54#55</t>
-  </si>
-  <si>
-    <t>100504</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <t>133#135</t>
-  </si>
-  <si>
-    <t>131#51</t>
-  </si>
-  <si>
-    <t>100503</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
       <t>3</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <t>133#245</t>
-  </si>
-  <si>
-    <t>87#90</t>
-  </si>
-  <si>
-    <t>100502</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
   </si>
   <si>
     <t>166#164</t>
@@ -1458,22 +1329,7 @@
     <t>100501</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
+    <t>Lost Tower 2</t>
   </si>
   <si>
     <t>从失落之塔1到失落之塔2</t>
@@ -1488,7 +1344,7 @@
     <t>100302</t>
   </si>
   <si>
-    <t>失落之塔</t>
+    <t>Lost Tower</t>
   </si>
   <si>
     <t>从冰风谷到失落之塔</t>
@@ -1503,7 +1359,7 @@
     <t>105202</t>
   </si>
   <si>
-    <t>亚特兰蒂斯</t>
+    <t>Atlantis</t>
   </si>
   <si>
     <t>从幻术园到亚特兰蒂斯</t>
@@ -2909,7 +2765,7 @@
       <c r="B5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2947,7 +2803,7 @@
       <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2985,7 +2841,7 @@
       <c r="B7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>56</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -3026,7 +2882,7 @@
       <c r="B8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -3067,7 +2923,7 @@
       <c r="B9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="5" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -3257,7 +3113,7 @@
       <c r="B14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="5" t="s">
         <v>93</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -3298,7 +3154,7 @@
       <c r="B15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="5" t="s">
         <v>93</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -3339,7 +3195,7 @@
       <c r="B16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="5" t="s">
         <v>93</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -3377,7 +3233,7 @@
       <c r="B17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="5" t="s">
         <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -3409,7 +3265,7 @@
       <c r="B18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="5" t="s">
         <v>112</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -3447,7 +3303,7 @@
       <c r="B19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="5" t="s">
         <v>112</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -3488,7 +3344,7 @@
       <c r="B20" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="5" t="s">
         <v>129</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -3529,7 +3385,7 @@
       <c r="B21" s="1">
         <v>1008</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="5" t="s">
         <v>129</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -3570,7 +3426,7 @@
       <c r="B22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="5" t="s">
         <v>142</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -3602,7 +3458,7 @@
       <c r="B23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="5" t="s">
         <v>149</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -3643,7 +3499,7 @@
       <c r="B24" s="1">
         <v>1009</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="5" t="s">
         <v>149</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -3684,7 +3540,7 @@
       <c r="B25" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -3725,7 +3581,7 @@
       <c r="B26" s="1">
         <v>1102</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="5" t="s">
         <v>168</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -3763,8 +3619,8 @@
       <c r="B27" s="1">
         <v>1102</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>174</v>
+      <c r="C27" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>169</v>
@@ -3773,7 +3629,7 @@
         <v>170</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>47</v>
@@ -3791,7 +3647,7 @@
         <v>1202</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>50</v>
@@ -3799,22 +3655,22 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B28" s="1">
         <v>1102</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>47</v>
@@ -3829,7 +3685,7 @@
         <v>70</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>50</v>
@@ -3837,22 +3693,22 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B29" s="1">
         <v>1002</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>47</v>
@@ -3870,7 +3726,7 @@
         <v>1102</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>50</v>
@@ -3878,22 +3734,22 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>47</v>
@@ -3902,13 +3758,13 @@
         <v>54</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>50</v>
@@ -3921,17 +3777,17 @@
       <c r="B31" s="1">
         <v>1202</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>193</v>
+      <c r="C31" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>47</v>
@@ -3940,7 +3796,7 @@
         <v>54</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>103</v>
@@ -3949,7 +3805,7 @@
         <v>1102</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>50</v>
@@ -3962,17 +3818,17 @@
       <c r="B32" s="1">
         <v>1202</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>193</v>
+      <c r="C32" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>47</v>
@@ -3981,13 +3837,13 @@
         <v>54</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="K32" s="1">
         <v>1102</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>50</v>
@@ -3995,31 +3851,31 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="G33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>50</v>
@@ -4027,22 +3883,22 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="D34" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="F34" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>47</v>
@@ -4057,10 +3913,10 @@
         <v>103</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>50</v>
@@ -4068,22 +3924,22 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>217</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>47</v>
@@ -4098,10 +3954,10 @@
         <v>103</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>50</v>
@@ -4109,22 +3965,22 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>47</v>
@@ -4133,16 +3989,16 @@
         <v>54</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>50</v>
@@ -4150,22 +4006,22 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>47</v>
@@ -4174,13 +4030,13 @@
         <v>54</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>50</v>
@@ -4188,22 +4044,22 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>47</v>
@@ -4218,10 +4074,10 @@
         <v>103</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>50</v>
@@ -4229,22 +4085,22 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>47</v>
@@ -4253,16 +4109,16 @@
         <v>54</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>60</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>50</v>
@@ -4270,22 +4126,22 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>47</v>
@@ -4297,13 +4153,13 @@
         <v>48</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>50</v>
@@ -4311,22 +4167,22 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>47</v>
@@ -4338,13 +4194,13 @@
         <v>48</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>50</v>
@@ -4358,16 +4214,16 @@
         <v>1157</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>47</v>
@@ -4382,7 +4238,7 @@
         <v>1157</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>50</v>
@@ -4396,16 +4252,16 @@
         <v>1157</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>47</v>
@@ -4420,7 +4276,7 @@
         <v>1157</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>50</v>
@@ -4434,16 +4290,16 @@
         <v>1157</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>47</v>
@@ -4458,7 +4314,7 @@
         <v>1157</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>50</v>
@@ -4472,16 +4328,16 @@
         <v>1157</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>47</v>
@@ -4496,7 +4352,7 @@
         <v>1157</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>50</v>
@@ -4510,16 +4366,16 @@
         <v>1157</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>47</v>
@@ -4534,7 +4390,7 @@
         <v>1157</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>50</v>
@@ -4548,16 +4404,16 @@
         <v>1157</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>47</v>
@@ -4572,7 +4428,7 @@
         <v>1157</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>50</v>
@@ -4586,16 +4442,16 @@
         <v>1157</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>47</v>
@@ -4610,7 +4466,7 @@
         <v>1157</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>50</v>
@@ -4624,16 +4480,16 @@
         <v>1157</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>47</v>
@@ -4648,7 +4504,7 @@
         <v>1157</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>50</v>
@@ -4656,22 +4512,22 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B50" s="1">
         <v>1505</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>47</v>
@@ -4680,7 +4536,7 @@
         <v>1605</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>50</v>
@@ -4688,22 +4544,22 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B51" s="1">
         <v>1405</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>255</v>
+      <c r="C51" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>47</v>
@@ -4712,7 +4568,7 @@
         <v>1505</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>50</v>
@@ -4720,22 +4576,22 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B52" s="1">
         <v>1305</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>260</v>
+      <c r="C52" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>47</v>
@@ -4744,7 +4600,7 @@
         <v>1405</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>50</v>
@@ -4752,22 +4608,22 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B53" s="1">
         <v>1205</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>265</v>
+      <c r="C53" s="5" t="s">
+        <v>262</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>47</v>
@@ -4776,7 +4632,7 @@
         <v>1305</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>50</v>
@@ -4784,22 +4640,22 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B54" s="1">
         <v>1105</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>270</v>
+      <c r="C54" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>47</v>
@@ -4808,7 +4664,7 @@
         <v>1205</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>50</v>
@@ -4816,22 +4672,22 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B55" s="1">
         <v>1005</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>275</v>
+      <c r="C55" s="5" t="s">
+        <v>272</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>47</v>
@@ -4849,7 +4705,7 @@
         <v>1105</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>50</v>
@@ -4857,22 +4713,22 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>280</v>
+      <c r="C56" s="5" t="s">
+        <v>277</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>47</v>
@@ -4881,7 +4737,7 @@
         <v>118</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>50</v>
@@ -4889,22 +4745,22 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>47</v>
@@ -4922,7 +4778,7 @@
         <v>100</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>50</v>
@@ -4930,22 +4786,22 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>285</v>
+      <c r="C58" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>47</v>
@@ -4954,16 +4810,16 @@
         <v>54</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>100</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>50</v>
@@ -4971,22 +4827,22 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>285</v>
+      <c r="C59" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>47</v>
@@ -5004,7 +4860,7 @@
         <v>100</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>50</v>
@@ -5017,7 +4873,7 @@
       <c r="B60" s="1">
         <v>16001</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -5055,7 +4911,7 @@
       <c r="B61" s="1">
         <v>16001</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D61" s="1" t="s">

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_transfer_point.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_transfer_point.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18585" windowHeight="11175"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_transfer_point" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_transfer_point!$A$4:$M$61</definedName>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="321">
   <si>
     <t>编号id</t>
   </si>
@@ -224,1184 +230,1391 @@
     <t>1031</t>
   </si>
   <si>
+    <t>罗兰峡谷</t>
+  </si>
+  <si>
+    <t>从罗兰峡谷到罗兰峡谷</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=0</t>
+  </si>
+  <si>
+    <t>160#204</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>0#0.5#0</t>
+  </si>
+  <si>
+    <t>94#237</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>103101</t>
+  </si>
+  <si>
+    <t>94#242</t>
+  </si>
+  <si>
+    <t>167#204</t>
+  </si>
+  <si>
+    <t>100401</t>
+  </si>
+  <si>
+    <t>1004</t>
+  </si>
+  <si>
+    <t>勇者大陆</t>
+  </si>
+  <si>
+    <t>从仙踪林到勇者大陆</t>
+  </si>
+  <si>
+    <t>151#3</t>
+  </si>
+  <si>
+    <t>3.5#0.5#0</t>
+  </si>
+  <si>
+    <t>0#-90#0</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>216#241</t>
+  </si>
+  <si>
+    <t>100301</t>
+  </si>
+  <si>
+    <t>1003</t>
+  </si>
+  <si>
+    <t>从冰风谷到勇者大陆</t>
+  </si>
+  <si>
+    <t>244#35</t>
+  </si>
+  <si>
+    <t>0#1#0</t>
+  </si>
+  <si>
+    <t>10#39</t>
+  </si>
+  <si>
+    <t>100201</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+  <si>
+    <t>从地下城到勇者大陆</t>
+  </si>
+  <si>
+    <t>108#248</t>
+  </si>
+  <si>
+    <t>1#0.5#-1.5</t>
+  </si>
+  <si>
+    <t>122#229</t>
+  </si>
+  <si>
+    <t>战盟BOSS5层</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战盟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BOSS4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层到战盟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BOSS5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+  </si>
+  <si>
+    <t>187#187</t>
+  </si>
+  <si>
+    <t>76#174</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战盟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BOSS4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战盟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BOSS3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层到战盟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BOSS4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+  </si>
+  <si>
+    <t>239#96</t>
+  </si>
+  <si>
+    <t>183#174</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战盟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BOSS3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战盟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BOSS2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层到战盟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>BOSS3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层</t>
+    </r>
+  </si>
+  <si>
+    <t>133#96</t>
+  </si>
+  <si>
+    <t>236#82</t>
+  </si>
+  <si>
+    <t>战盟BOSS2层</t>
+  </si>
+  <si>
+    <t>战盟BOSS1层到战盟BOSS2层</t>
+  </si>
+  <si>
+    <t>18#95</t>
+  </si>
+  <si>
+    <t>131#81</t>
+  </si>
+  <si>
+    <t>103401</t>
+  </si>
+  <si>
+    <t>1034</t>
+  </si>
+  <si>
+    <t>仙踪林</t>
+  </si>
+  <si>
+    <t>从幽暗森林到仙踪林</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=1</t>
+  </si>
+  <si>
+    <t>74#11</t>
+  </si>
+  <si>
+    <t>0#120#0</t>
+  </si>
+  <si>
+    <t>222#33</t>
+  </si>
+  <si>
+    <t>100801</t>
+  </si>
+  <si>
+    <t>1008</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从亚特兰蒂斯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到仙踪林</t>
+    </r>
+  </si>
+  <si>
+    <t>10#10</t>
+  </si>
+  <si>
+    <t>0#90#0</t>
+  </si>
+  <si>
+    <t>237#241</t>
+  </si>
+  <si>
+    <t>100103</t>
+  </si>
+  <si>
+    <t>从勇者大陆到仙踪林</t>
+  </si>
+  <si>
+    <t>215#246</t>
+  </si>
+  <si>
+    <t>1#1#-1.5</t>
+  </si>
+  <si>
+    <t>152#8</t>
+  </si>
+  <si>
+    <t>105201</t>
+  </si>
+  <si>
+    <t>1052</t>
+  </si>
+  <si>
+    <t>冰风谷</t>
+  </si>
+  <si>
+    <t>从幻术园到冰风谷</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=20</t>
+  </si>
+  <si>
+    <t>24#29</t>
+  </si>
+  <si>
+    <t>162#241</t>
+  </si>
+  <si>
+    <t>100507</t>
+  </si>
+  <si>
+    <t>1005</t>
+  </si>
+  <si>
+    <t>从失落之塔到冰风谷</t>
+  </si>
+  <si>
+    <t>164#0</t>
+  </si>
+  <si>
+    <t>1#0.5#0</t>
+  </si>
+  <si>
+    <t>6#246</t>
+  </si>
+  <si>
+    <t>100102</t>
+  </si>
+  <si>
+    <t>从勇者大陆到冰风谷</t>
+  </si>
+  <si>
+    <t>5#39</t>
+  </si>
+  <si>
+    <t>238#36</t>
+  </si>
+  <si>
+    <t>103801</t>
+  </si>
+  <si>
+    <t>1038</t>
+  </si>
+  <si>
+    <t>死亡沙漠</t>
+  </si>
+  <si>
+    <t>从坎特鲁废墟到死亡沙漠</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=130</t>
+  </si>
+  <si>
+    <t>18#221</t>
+  </si>
+  <si>
+    <t>0#160#0</t>
+  </si>
+  <si>
+    <t>1009</t>
+  </si>
+  <si>
+    <t>11#200</t>
+  </si>
+  <si>
+    <t>100802</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从亚特兰蒂斯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到死亡沙漠</t>
+    </r>
+  </si>
+  <si>
+    <t>14#227</t>
+  </si>
+  <si>
+    <t>0#1.5#-1</t>
+  </si>
+  <si>
+    <t>241#43</t>
+  </si>
+  <si>
+    <t>100403</t>
+  </si>
+  <si>
+    <t>幽暗森林</t>
+  </si>
+  <si>
+    <t>从仙踪林到幽暗森林</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=170</t>
+  </si>
+  <si>
+    <t>223#30</t>
+  </si>
+  <si>
+    <t>78#10</t>
+  </si>
+  <si>
+    <t>103901</t>
+  </si>
+  <si>
+    <t>1039</t>
+  </si>
+  <si>
+    <t>坎特鲁废墟</t>
+  </si>
+  <si>
+    <t>从坎特鲁遗址到坎特鲁废墟</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=250</t>
+  </si>
+  <si>
+    <t>69#105</t>
+  </si>
+  <si>
+    <t>0#110#0</t>
+  </si>
+  <si>
+    <t>82#91</t>
+  </si>
+  <si>
+    <t>100902</t>
+  </si>
+  <si>
+    <t>从死亡沙漠到坎特鲁废墟</t>
+  </si>
+  <si>
+    <t>6#200</t>
+  </si>
+  <si>
+    <t>0#0.5#-2</t>
+  </si>
+  <si>
+    <t>20#218</t>
+  </si>
+  <si>
+    <t>103802</t>
+  </si>
+  <si>
+    <t>坎特鲁遗址</t>
+  </si>
+  <si>
+    <t>从坎特鲁废墟到坎特鲁遗址</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=290</t>
+  </si>
+  <si>
+    <t>89#90</t>
+  </si>
+  <si>
+    <t>0#-80#0</t>
+  </si>
+  <si>
+    <t>74#106</t>
+  </si>
+  <si>
+    <t>100206</t>
+  </si>
+  <si>
+    <t>地下城3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>checkLevel&gt;=30</t>
+  </si>
+  <si>
+    <t>5#33</t>
+  </si>
+  <si>
+    <t>29#119</t>
+  </si>
+  <si>
+    <t>100204</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>2#17</t>
+  </si>
+  <si>
+    <t>7#85</t>
+  </si>
+  <si>
+    <t>100203</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>232#128</t>
+  </si>
+  <si>
+    <t>243#149</t>
+  </si>
+  <si>
+    <t>100202</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从地下城</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到地下城2</t>
+    </r>
+  </si>
+  <si>
+    <t>239#149</t>
+  </si>
+  <si>
+    <t>233#123</t>
+  </si>
+  <si>
+    <t>100101</t>
+  </si>
+  <si>
+    <t>地下城</t>
+  </si>
+  <si>
+    <t>从勇者大陆到地下城</t>
+  </si>
+  <si>
+    <t>122#232</t>
+  </si>
+  <si>
+    <t>0.5#0.5#-2</t>
+  </si>
+  <si>
+    <t>110#245</t>
+  </si>
+  <si>
+    <t>地下城2</t>
+  </si>
+  <si>
+    <t>从地下城3到地下城2</t>
+  </si>
+  <si>
+    <t>2#85</t>
+  </si>
+  <si>
+    <t>0#0.5#-1</t>
+  </si>
+  <si>
+    <t>7#18</t>
+  </si>
+  <si>
+    <t>29#127</t>
+  </si>
+  <si>
+    <t>1#0.5#-2.5</t>
+  </si>
+  <si>
+    <t>8#28</t>
+  </si>
+  <si>
+    <t>100304</t>
+  </si>
+  <si>
+    <t>冰霜之城</t>
+  </si>
+  <si>
+    <t>从冰风谷到冰霜之城</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=330</t>
+  </si>
+  <si>
+    <t>53#92</t>
+  </si>
+  <si>
+    <t>1058</t>
+  </si>
+  <si>
+    <t>224#209</t>
+  </si>
+  <si>
+    <t>105708</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>安宁池</t>
+  </si>
+  <si>
+    <t>从安宁池上岛到安宁池左上</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=350</t>
+  </si>
+  <si>
+    <t>57#176</t>
+  </si>
+  <si>
+    <t>138#109</t>
+  </si>
+  <si>
+    <t>105707</t>
+  </si>
+  <si>
+    <t>从安宁池左上到安宁池上岛</t>
+  </si>
+  <si>
+    <t>124#109</t>
+  </si>
+  <si>
+    <t>64#177</t>
+  </si>
+  <si>
+    <t>105706</t>
+  </si>
+  <si>
+    <t>从安宁池左岛到安宁池左上</t>
+  </si>
+  <si>
+    <t>68#52</t>
+  </si>
+  <si>
+    <t>2#1#0</t>
+  </si>
+  <si>
+    <t>0#-120#0</t>
+  </si>
+  <si>
+    <t>105705</t>
+  </si>
+  <si>
+    <t>从安宁池左下到安宁池左岛</t>
+  </si>
+  <si>
+    <t>139#95</t>
+  </si>
+  <si>
+    <t>2#0.5#-1.5</t>
+  </si>
+  <si>
+    <t>66#46</t>
+  </si>
+  <si>
+    <t>105704</t>
+  </si>
+  <si>
+    <t>从安宁池下岛到安宁池右下</t>
+  </si>
+  <si>
+    <t>197#13</t>
+  </si>
+  <si>
+    <t>105703</t>
+  </si>
+  <si>
+    <t>从安宁池右下到安宁池下岛</t>
+  </si>
+  <si>
+    <t>149#109</t>
+  </si>
+  <si>
+    <t>204#12</t>
+  </si>
+  <si>
+    <t>105702</t>
+  </si>
+  <si>
+    <t>从安宁池右岛到安宁池右上</t>
+  </si>
+  <si>
+    <t>185#187</t>
+  </si>
+  <si>
+    <t>0#60#0</t>
+  </si>
+  <si>
+    <t>105701</t>
+  </si>
+  <si>
+    <t>从安宁池右上到安宁池右岛</t>
+  </si>
+  <si>
+    <t>139#125</t>
+  </si>
+  <si>
+    <t>0#180#0</t>
+  </si>
+  <si>
+    <t>191#191</t>
+  </si>
+  <si>
+    <t>黄金安宁池</t>
+  </si>
+  <si>
+    <t>从黄金安宁池到黄金安宁池</t>
+  </si>
+  <si>
+    <t>100506</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <t>checkLevel&gt;=40</t>
+  </si>
+  <si>
+    <t>6#6</t>
+  </si>
+  <si>
+    <t>9#87</t>
+  </si>
+  <si>
+    <t>100505</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <t>从失落之塔5到失落之塔6</t>
+  </si>
+  <si>
+    <t>131#16</t>
+  </si>
+  <si>
+    <t>54#55</t>
+  </si>
+  <si>
+    <t>100504</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <t>133#135</t>
+  </si>
+  <si>
+    <t>131#51</t>
+  </si>
+  <si>
+    <t>100503</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <t>133#245</t>
+  </si>
+  <si>
+    <t>87#90</t>
+  </si>
+  <si>
+    <t>100502</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>166#164</t>
+  </si>
+  <si>
+    <t>86#168</t>
+  </si>
+  <si>
+    <t>100501</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>失落之塔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>从失落之塔1到失落之塔2</t>
+  </si>
+  <si>
+    <t>190#7</t>
+  </si>
+  <si>
+    <t>248#240</t>
+  </si>
+  <si>
+    <t>100302</t>
+  </si>
+  <si>
+    <t>失落之塔</t>
+  </si>
+  <si>
+    <t>从冰风谷到失落之塔</t>
+  </si>
+  <si>
+    <t>2#248</t>
+  </si>
+  <si>
+    <t>164#5</t>
+  </si>
+  <si>
+    <t>105202</t>
+  </si>
+  <si>
+    <t>亚特兰蒂斯</t>
+  </si>
+  <si>
+    <t>从幻术园到亚特兰蒂斯</t>
+  </si>
+  <si>
+    <t>checkLevel&gt;=70</t>
+  </si>
+  <si>
+    <t>247#149</t>
+  </si>
+  <si>
+    <t>17#19</t>
+  </si>
+  <si>
+    <t>100901</t>
+  </si>
+  <si>
+    <t>从死亡沙漠到亚特兰蒂斯</t>
+  </si>
+  <si>
+    <t>246#42</t>
+  </si>
+  <si>
+    <t>0#0.5#-2.5</t>
+  </si>
+  <si>
+    <t>0#-30#0</t>
+  </si>
+  <si>
+    <t>20#227</t>
+  </si>
+  <si>
+    <t>100402</t>
+  </si>
+  <si>
+    <t>从仙踪林到亚特兰蒂斯</t>
+  </si>
+  <si>
+    <t>243#241</t>
+  </si>
+  <si>
+    <t>15#11</t>
+  </si>
+  <si>
     <t>Loren Castle Siege</t>
   </si>
   <si>
-    <t>从罗兰峡谷到罗兰峡谷</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=0</t>
-  </si>
-  <si>
-    <t>160#204</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>0#0.5#0</t>
-  </si>
-  <si>
-    <t>94#237</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>103101</t>
-  </si>
-  <si>
-    <t>94#242</t>
-  </si>
-  <si>
-    <t>167#204</t>
-  </si>
-  <si>
-    <t>100401</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
     <t>Lorencia</t>
   </si>
   <si>
-    <t>从仙踪林到勇者大陆</t>
-  </si>
-  <si>
-    <t>151#3</t>
-  </si>
-  <si>
-    <t>3.5#0.5#0</t>
-  </si>
-  <si>
-    <t>0#-90#0</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>216#241</t>
-  </si>
-  <si>
-    <t>100301</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>从冰风谷到勇者大陆</t>
-  </si>
-  <si>
-    <t>244#35</t>
-  </si>
-  <si>
-    <t>0#1#0</t>
-  </si>
-  <si>
-    <t>10#39</t>
-  </si>
-  <si>
-    <t>100201</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>从地下城到勇者大陆</t>
-  </si>
-  <si>
-    <t>108#248</t>
-  </si>
-  <si>
-    <t>1#0.5#-1.5</t>
-  </si>
-  <si>
-    <t>122#229</t>
-  </si>
-  <si>
-    <t>战盟BOSS5层</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>战盟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOSS4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层到战盟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOSS5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层</t>
-    </r>
-  </si>
-  <si>
-    <t>187#187</t>
-  </si>
-  <si>
-    <t>76#174</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>战盟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOSS4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>战盟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOSS3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层到战盟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOSS4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层</t>
-    </r>
-  </si>
-  <si>
-    <t>239#96</t>
-  </si>
-  <si>
-    <t>183#174</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>战盟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOSS3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>战盟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOSS2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层到战盟</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BOSS3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层</t>
-    </r>
-  </si>
-  <si>
-    <t>133#96</t>
-  </si>
-  <si>
-    <t>236#82</t>
-  </si>
-  <si>
-    <t>战盟BOSS2层</t>
-  </si>
-  <si>
-    <t>战盟BOSS1层到战盟BOSS2层</t>
-  </si>
-  <si>
-    <t>18#95</t>
-  </si>
-  <si>
-    <t>131#81</t>
-  </si>
-  <si>
-    <t>103401</t>
-  </si>
-  <si>
-    <t>1034</t>
-  </si>
-  <si>
     <t>Noria</t>
   </si>
   <si>
-    <t>从幽暗森林到仙踪林</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=1</t>
-  </si>
-  <si>
-    <t>74#11</t>
-  </si>
-  <si>
-    <t>0#120#0</t>
-  </si>
-  <si>
-    <t>222#33</t>
-  </si>
-  <si>
-    <t>100801</t>
-  </si>
-  <si>
-    <t>1008</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从亚特兰蒂斯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到仙踪林</t>
-    </r>
-  </si>
-  <si>
-    <t>10#10</t>
-  </si>
-  <si>
-    <t>0#90#0</t>
-  </si>
-  <si>
-    <t>237#241</t>
-  </si>
-  <si>
-    <t>100103</t>
-  </si>
-  <si>
-    <t>从勇者大陆到仙踪林</t>
-  </si>
-  <si>
-    <t>215#246</t>
-  </si>
-  <si>
-    <t>1#1#-1.5</t>
-  </si>
-  <si>
-    <t>152#8</t>
-  </si>
-  <si>
-    <t>105201</t>
-  </si>
-  <si>
-    <t>1052</t>
-  </si>
-  <si>
     <t>Devias</t>
   </si>
   <si>
-    <t>从幻术园到冰风谷</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=20</t>
-  </si>
-  <si>
-    <t>24#29</t>
-  </si>
-  <si>
-    <t>162#241</t>
-  </si>
-  <si>
-    <t>100507</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>从失落之塔到冰风谷</t>
-  </si>
-  <si>
-    <t>164#0</t>
-  </si>
-  <si>
-    <t>1#0.5#0</t>
-  </si>
-  <si>
-    <t>6#246</t>
-  </si>
-  <si>
-    <t>100102</t>
-  </si>
-  <si>
-    <t>从勇者大陆到冰风谷</t>
-  </si>
-  <si>
-    <t>5#39</t>
-  </si>
-  <si>
-    <t>238#36</t>
-  </si>
-  <si>
-    <t>103801</t>
-  </si>
-  <si>
-    <t>1038</t>
-  </si>
-  <si>
     <t>Desert</t>
   </si>
   <si>
-    <t>从坎特鲁废墟到死亡沙漠</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=130</t>
-  </si>
-  <si>
-    <t>18#221</t>
-  </si>
-  <si>
-    <t>0#160#0</t>
-  </si>
-  <si>
-    <t>1009</t>
-  </si>
-  <si>
-    <t>11#200</t>
-  </si>
-  <si>
-    <t>100802</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从亚特兰蒂斯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到死亡沙漠</t>
-    </r>
-  </si>
-  <si>
-    <t>14#227</t>
-  </si>
-  <si>
-    <t>0#1.5#-1</t>
-  </si>
-  <si>
-    <t>241#43</t>
-  </si>
-  <si>
-    <t>100403</t>
-  </si>
-  <si>
     <t>Swamp of Calmness</t>
   </si>
   <si>
-    <t>从仙踪林到幽暗森林</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=170</t>
-  </si>
-  <si>
-    <t>223#30</t>
-  </si>
-  <si>
-    <t>78#10</t>
-  </si>
-  <si>
-    <t>103901</t>
-  </si>
-  <si>
-    <t>1039</t>
-  </si>
-  <si>
     <t>Kanturu Ruins</t>
   </si>
   <si>
-    <t>从坎特鲁遗址到坎特鲁废墟</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=250</t>
-  </si>
-  <si>
-    <t>69#105</t>
-  </si>
-  <si>
-    <t>0#110#0</t>
-  </si>
-  <si>
-    <t>82#91</t>
-  </si>
-  <si>
-    <t>100902</t>
-  </si>
-  <si>
-    <t>从死亡沙漠到坎特鲁废墟</t>
-  </si>
-  <si>
-    <t>6#200</t>
-  </si>
-  <si>
-    <t>0#0.5#-2</t>
-  </si>
-  <si>
-    <t>20#218</t>
-  </si>
-  <si>
-    <t>103802</t>
-  </si>
-  <si>
     <t>Kanturu Remain</t>
   </si>
   <si>
-    <t>从坎特鲁废墟到坎特鲁遗址</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=290</t>
-  </si>
-  <si>
-    <t>89#90</t>
-  </si>
-  <si>
-    <t>0#-80#0</t>
-  </si>
-  <si>
-    <t>74#106</t>
-  </si>
-  <si>
-    <t>100206</t>
-  </si>
-  <si>
     <t>Dungeon 3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从地下城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到地下城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>checkLevel&gt;=30</t>
-  </si>
-  <si>
-    <t>5#33</t>
-  </si>
-  <si>
-    <t>29#119</t>
-  </si>
-  <si>
-    <t>100204</t>
-  </si>
-  <si>
-    <t>2#17</t>
-  </si>
-  <si>
-    <t>7#85</t>
-  </si>
-  <si>
-    <t>100203</t>
-  </si>
-  <si>
     <t>Dungeon 1</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从地下城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到地下城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>232#128</t>
-  </si>
-  <si>
-    <t>243#149</t>
-  </si>
-  <si>
-    <t>100202</t>
-  </si>
-  <si>
     <t>Dungeon 2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从地下城</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到地下城2</t>
-    </r>
-  </si>
-  <si>
-    <t>239#149</t>
-  </si>
-  <si>
-    <t>233#123</t>
-  </si>
-  <si>
-    <t>100101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dungeon </t>
   </si>
   <si>
-    <t>从勇者大陆到地下城</t>
-  </si>
-  <si>
-    <t>122#232</t>
-  </si>
-  <si>
-    <t>0.5#0.5#-2</t>
-  </si>
-  <si>
-    <t>110#245</t>
-  </si>
-  <si>
-    <t>从地下城3到地下城2</t>
-  </si>
-  <si>
-    <t>2#85</t>
-  </si>
-  <si>
-    <t>0#0.5#-1</t>
-  </si>
-  <si>
-    <t>7#18</t>
-  </si>
-  <si>
-    <t>29#127</t>
-  </si>
-  <si>
-    <t>1#0.5#-2.5</t>
-  </si>
-  <si>
-    <t>8#28</t>
-  </si>
-  <si>
-    <t>100304</t>
-  </si>
-  <si>
     <t>Ice Castle</t>
   </si>
   <si>
-    <t>从冰风谷到冰霜之城</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=330</t>
-  </si>
-  <si>
-    <t>53#92</t>
-  </si>
-  <si>
-    <t>1058</t>
-  </si>
-  <si>
-    <t>224#209</t>
-  </si>
-  <si>
-    <t>105708</t>
-  </si>
-  <si>
-    <t>1057</t>
-  </si>
-  <si>
     <t>Aida</t>
   </si>
   <si>
-    <t>从安宁池上岛到安宁池左上</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=350</t>
-  </si>
-  <si>
-    <t>57#176</t>
-  </si>
-  <si>
-    <t>138#109</t>
-  </si>
-  <si>
-    <t>105707</t>
-  </si>
-  <si>
-    <t>从安宁池左上到安宁池上岛</t>
-  </si>
-  <si>
-    <t>124#109</t>
-  </si>
-  <si>
-    <t>64#177</t>
-  </si>
-  <si>
-    <t>105706</t>
-  </si>
-  <si>
-    <t>从安宁池左岛到安宁池左上</t>
-  </si>
-  <si>
-    <t>68#52</t>
-  </si>
-  <si>
-    <t>2#1#0</t>
-  </si>
-  <si>
-    <t>0#-120#0</t>
-  </si>
-  <si>
-    <t>105705</t>
-  </si>
-  <si>
-    <t>从安宁池左下到安宁池左岛</t>
-  </si>
-  <si>
-    <t>139#95</t>
-  </si>
-  <si>
-    <t>2#0.5#-1.5</t>
-  </si>
-  <si>
-    <t>66#46</t>
-  </si>
-  <si>
-    <t>105704</t>
-  </si>
-  <si>
-    <t>从安宁池下岛到安宁池右下</t>
-  </si>
-  <si>
-    <t>197#13</t>
-  </si>
-  <si>
-    <t>105703</t>
-  </si>
-  <si>
-    <t>从安宁池右下到安宁池下岛</t>
-  </si>
-  <si>
-    <t>149#109</t>
-  </si>
-  <si>
-    <t>204#12</t>
-  </si>
-  <si>
-    <t>105702</t>
-  </si>
-  <si>
-    <t>从安宁池右岛到安宁池右上</t>
-  </si>
-  <si>
-    <t>185#187</t>
-  </si>
-  <si>
-    <t>0#60#0</t>
-  </si>
-  <si>
-    <t>105701</t>
-  </si>
-  <si>
-    <t>从安宁池右上到安宁池右岛</t>
-  </si>
-  <si>
-    <t>139#125</t>
-  </si>
-  <si>
-    <t>0#180#0</t>
-  </si>
-  <si>
-    <t>191#191</t>
-  </si>
-  <si>
-    <t>黄金安宁池</t>
-  </si>
-  <si>
-    <t>从黄金安宁池到黄金安宁池</t>
-  </si>
-  <si>
-    <t>100506</t>
-  </si>
-  <si>
     <t>Lost Tower 7</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
-    <t>checkLevel&gt;=40</t>
-  </si>
-  <si>
-    <t>6#6</t>
-  </si>
-  <si>
-    <t>9#87</t>
-  </si>
-  <si>
-    <t>100505</t>
-  </si>
-  <si>
     <t>Lost Tower 6</t>
   </si>
   <si>
-    <t>从失落之塔5到失落之塔6</t>
-  </si>
-  <si>
-    <t>131#16</t>
-  </si>
-  <si>
-    <t>54#55</t>
-  </si>
-  <si>
-    <t>100504</t>
-  </si>
-  <si>
     <t>Lost Tower 5</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <t>133#135</t>
-  </si>
-  <si>
-    <t>131#51</t>
-  </si>
-  <si>
-    <t>100503</t>
-  </si>
-  <si>
     <t>Lost Tower 4</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <t>133#245</t>
-  </si>
-  <si>
-    <t>87#90</t>
-  </si>
-  <si>
-    <t>100502</t>
-  </si>
-  <si>
     <t>Lost Tower 3</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>从失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到失落之塔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>166#164</t>
-  </si>
-  <si>
-    <t>86#168</t>
-  </si>
-  <si>
-    <t>100501</t>
-  </si>
-  <si>
     <t>Lost Tower 2</t>
   </si>
   <si>
-    <t>从失落之塔1到失落之塔2</t>
-  </si>
-  <si>
-    <t>190#7</t>
-  </si>
-  <si>
-    <t>248#240</t>
-  </si>
-  <si>
-    <t>100302</t>
-  </si>
-  <si>
     <t>Lost Tower</t>
   </si>
   <si>
-    <t>从冰风谷到失落之塔</t>
-  </si>
-  <si>
-    <t>2#248</t>
-  </si>
-  <si>
-    <t>164#5</t>
-  </si>
-  <si>
-    <t>105202</t>
-  </si>
-  <si>
     <t>Atlantis</t>
-  </si>
-  <si>
-    <t>从幻术园到亚特兰蒂斯</t>
-  </si>
-  <si>
-    <t>checkLevel&gt;=70</t>
-  </si>
-  <si>
-    <t>247#149</t>
-  </si>
-  <si>
-    <t>17#19</t>
-  </si>
-  <si>
-    <t>100901</t>
-  </si>
-  <si>
-    <t>从死亡沙漠到亚特兰蒂斯</t>
-  </si>
-  <si>
-    <t>246#42</t>
-  </si>
-  <si>
-    <t>0#0.5#-2.5</t>
-  </si>
-  <si>
-    <t>0#-30#0</t>
-  </si>
-  <si>
-    <t>20#227</t>
-  </si>
-  <si>
-    <t>100402</t>
-  </si>
-  <si>
-    <t>从仙踪林到亚特兰蒂斯</t>
-  </si>
-  <si>
-    <t>243#241</t>
-  </si>
-  <si>
-    <t>15#11</t>
   </si>
 </sst>
 </file>
@@ -2586,18 +2799,18 @@
   <dimension ref="A1:M72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.71428571428571" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="26.2857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="105.714285714286" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.8571428571429" style="1" customWidth="1"/>
-    <col min="7" max="11" width="9" style="1"/>
-    <col min="12" max="12" width="14.7142857142857" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="8.81904761904762" customWidth="1"/>
+    <col min="2" max="2" width="10.2857142857143"/>
+    <col min="3" max="3" width="30.0380952380952" customWidth="1"/>
+    <col min="4" max="4" width="120.819047619048" customWidth="1"/>
+    <col min="5" max="5" width="19.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="12.4095238095238" customWidth="1"/>
+    <col min="7" max="11" width="10.2857142857143"/>
+    <col min="12" max="12" width="16.8190476190476" customWidth="1"/>
+    <col min="13" max="16384" width="10.2857142857143"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2676,7 +2889,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" customFormat="1" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -2717,7 +2930,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" customFormat="1" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2758,14 +2971,14 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" customFormat="1" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2796,14 +3009,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" customFormat="1" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2834,14 +3047,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" customFormat="1" spans="1:13">
       <c r="A7" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2875,14 +3088,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" customFormat="1" spans="1:13">
       <c r="A8" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2916,14 +3129,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" customFormat="1" spans="1:13">
       <c r="A9" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="1" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2954,7 +3167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" customFormat="1" spans="1:13">
       <c r="A10" s="1">
         <v>101304</v>
       </c>
@@ -2992,7 +3205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" customFormat="1" spans="1:13">
       <c r="A11" s="1">
         <v>101303</v>
       </c>
@@ -3030,7 +3243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" customFormat="1" spans="1:13">
       <c r="A12" s="1">
         <v>101302</v>
       </c>
@@ -3068,7 +3281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1" spans="1:13">
+    <row r="13" customFormat="1" ht="14" customHeight="1" spans="1:13">
       <c r="A13" s="1">
         <v>101301</v>
       </c>
@@ -3106,14 +3319,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" customFormat="1" spans="1:13">
       <c r="A14" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -3147,14 +3360,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" customFormat="1" spans="1:13">
       <c r="A15" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -3188,14 +3401,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" customFormat="1" spans="1:13">
       <c r="A16" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="1" t="s">
         <v>93</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -3226,14 +3439,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" customFormat="1" spans="1:13">
       <c r="A17" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -3258,14 +3471,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" customFormat="1" spans="1:13">
       <c r="A18" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -3296,14 +3509,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" customFormat="1" spans="1:13">
       <c r="A19" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -3337,14 +3550,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" customFormat="1" spans="1:13">
       <c r="A20" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -3378,14 +3591,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" customFormat="1" spans="1:13">
       <c r="A21" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B21" s="1">
         <v>1008</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="1" t="s">
         <v>129</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -3419,14 +3632,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" customFormat="1" spans="1:13">
       <c r="A22" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -3451,14 +3664,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" customFormat="1" spans="1:13">
       <c r="A23" s="1" t="s">
         <v>147</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="1" t="s">
         <v>149</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -3492,14 +3705,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" customFormat="1" spans="1:13">
       <c r="A24" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B24" s="1">
         <v>1009</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="1" t="s">
         <v>149</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -3533,14 +3746,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" customFormat="1" spans="1:13">
       <c r="A25" s="1" t="s">
         <v>160</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="1" t="s">
         <v>161</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -3574,14 +3787,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" customFormat="1" spans="1:13">
       <c r="A26" s="1" t="s">
         <v>167</v>
       </c>
       <c r="B26" s="1">
         <v>1102</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -3612,15 +3825,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" customFormat="1" spans="1:13">
       <c r="A27" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B27" s="1">
         <v>1102</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>168</v>
+      <c r="C27" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>169</v>
@@ -3629,7 +3842,7 @@
         <v>170</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>47</v>
@@ -3647,30 +3860,30 @@
         <v>1202</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" customFormat="1" spans="1:13">
       <c r="A28" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B28" s="1">
         <v>1102</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>177</v>
+      <c r="C28" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>47</v>
@@ -3685,30 +3898,30 @@
         <v>70</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" customFormat="1" spans="1:13">
       <c r="A29" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B29" s="1">
         <v>1002</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>182</v>
+      <c r="C29" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>47</v>
@@ -3726,30 +3939,30 @@
         <v>1102</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" customFormat="1" spans="1:13">
       <c r="A30" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>187</v>
+      <c r="C30" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>47</v>
@@ -3758,36 +3971,36 @@
         <v>54</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" customFormat="1" spans="1:13">
       <c r="A31" s="1">
         <v>100208</v>
       </c>
       <c r="B31" s="1">
         <v>1202</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>182</v>
+      <c r="C31" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>47</v>
@@ -3796,7 +4009,7 @@
         <v>54</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>103</v>
@@ -3805,30 +4018,30 @@
         <v>1102</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" customFormat="1" spans="1:13">
       <c r="A32" s="1">
         <v>100207</v>
       </c>
       <c r="B32" s="1">
         <v>1202</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>182</v>
+      <c r="C32" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>170</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>47</v>
@@ -3837,68 +4050,68 @@
         <v>54</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K32" s="1">
         <v>1102</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" customFormat="1" spans="1:13">
       <c r="A33" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>200</v>
+      <c r="C33" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>47</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" customFormat="1" spans="1:13">
       <c r="A34" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>47</v>
@@ -3913,33 +4126,33 @@
         <v>103</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L34" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:13">
+      <c r="A35" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>47</v>
@@ -3954,112 +4167,112 @@
         <v>103</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" customFormat="1" spans="1:13">
       <c r="A36" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" s="1">
+        <v>54</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:13">
+      <c r="A37" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" s="1">
-        <v>54</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L36" s="1" t="s">
+      <c r="D37" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="M36" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="1">
+        <v>54</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:13">
+      <c r="A38" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H37" s="1">
-        <v>54</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>208</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>47</v>
@@ -4074,33 +4287,33 @@
         <v>103</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L38" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:13">
+      <c r="A39" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="M38" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>47</v>
@@ -4109,39 +4322,39 @@
         <v>54</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>60</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" customFormat="1" spans="1:13">
       <c r="A40" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>47</v>
@@ -4153,36 +4366,36 @@
         <v>48</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:13">
+      <c r="A41" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="M40" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>47</v>
@@ -4194,19 +4407,19 @@
         <v>48</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" customFormat="1" spans="1:13">
       <c r="A42" s="1">
         <v>115708</v>
       </c>
@@ -4214,16 +4427,16 @@
         <v>1157</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>47</v>
@@ -4238,13 +4451,13 @@
         <v>1157</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" customFormat="1" spans="1:13">
       <c r="A43" s="1">
         <v>115707</v>
       </c>
@@ -4252,16 +4465,16 @@
         <v>1157</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>47</v>
@@ -4276,13 +4489,13 @@
         <v>1157</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" customFormat="1" spans="1:13">
       <c r="A44" s="1">
         <v>115706</v>
       </c>
@@ -4290,16 +4503,16 @@
         <v>1157</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>47</v>
@@ -4314,13 +4527,13 @@
         <v>1157</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" customFormat="1" spans="1:13">
       <c r="A45" s="1">
         <v>115705</v>
       </c>
@@ -4328,16 +4541,16 @@
         <v>1157</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>47</v>
@@ -4352,13 +4565,13 @@
         <v>1157</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" customFormat="1" spans="1:13">
       <c r="A46" s="1">
         <v>115704</v>
       </c>
@@ -4366,16 +4579,16 @@
         <v>1157</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>47</v>
@@ -4390,13 +4603,13 @@
         <v>1157</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" customFormat="1" spans="1:13">
       <c r="A47" s="1">
         <v>115703</v>
       </c>
@@ -4404,16 +4617,16 @@
         <v>1157</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>47</v>
@@ -4428,13 +4641,13 @@
         <v>1157</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" customFormat="1" spans="1:13">
       <c r="A48" s="1">
         <v>115702</v>
       </c>
@@ -4442,16 +4655,16 @@
         <v>1157</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>47</v>
@@ -4466,13 +4679,13 @@
         <v>1157</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" customFormat="1" spans="1:13">
       <c r="A49" s="1">
         <v>115701</v>
       </c>
@@ -4480,16 +4693,16 @@
         <v>1157</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>47</v>
@@ -4504,30 +4717,30 @@
         <v>1157</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" customFormat="1" spans="1:13">
       <c r="A50" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B50" s="1">
         <v>1505</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>246</v>
+      <c r="C50" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>47</v>
@@ -4536,30 +4749,30 @@
         <v>1605</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" customFormat="1" spans="1:13">
       <c r="A51" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B51" s="1">
         <v>1405</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>252</v>
+      <c r="C51" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>47</v>
@@ -4568,30 +4781,30 @@
         <v>1505</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" customFormat="1" spans="1:13">
       <c r="A52" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B52" s="1">
         <v>1305</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>257</v>
+      <c r="C52" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>47</v>
@@ -4600,30 +4813,30 @@
         <v>1405</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" customFormat="1" spans="1:13">
       <c r="A53" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B53" s="1">
         <v>1205</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>262</v>
+      <c r="C53" s="2" t="s">
+        <v>264</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>47</v>
@@ -4632,30 +4845,30 @@
         <v>1305</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" customFormat="1" spans="1:13">
       <c r="A54" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B54" s="1">
         <v>1105</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>267</v>
+      <c r="C54" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>47</v>
@@ -4664,30 +4877,30 @@
         <v>1205</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" customFormat="1" spans="1:13">
       <c r="A55" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B55" s="1">
         <v>1005</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>272</v>
+      <c r="C55" s="2" t="s">
+        <v>274</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>47</v>
@@ -4705,30 +4918,30 @@
         <v>1105</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" customFormat="1" spans="1:13">
       <c r="A56" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>277</v>
+      <c r="C56" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>47</v>
@@ -4737,30 +4950,30 @@
         <v>118</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" customFormat="1" spans="1:13">
       <c r="A57" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>282</v>
+      <c r="C57" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>47</v>
@@ -4778,30 +4991,30 @@
         <v>100</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" customFormat="1" spans="1:13">
       <c r="A58" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>282</v>
+      <c r="C58" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>47</v>
@@ -4810,39 +5023,39 @@
         <v>54</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>100</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" customFormat="1" spans="1:13">
       <c r="A59" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>282</v>
+      <c r="C59" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>47</v>
@@ -4860,20 +5073,20 @@
         <v>100</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" customFormat="1" spans="1:13">
       <c r="A60" s="1">
         <v>1600101</v>
       </c>
       <c r="B60" s="1">
         <v>16001</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -4904,14 +5117,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" customFormat="1" spans="1:13">
       <c r="A61" s="1">
         <v>1600102</v>
       </c>
       <c r="B61" s="1">
         <v>16001</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -4942,16 +5155,16 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="7:7">
+    <row r="69" customFormat="1" spans="7:7">
       <c r="G69" s="2"/>
     </row>
-    <row r="70" spans="7:7">
+    <row r="70" customFormat="1" spans="7:7">
       <c r="G70" s="2"/>
     </row>
-    <row r="71" spans="7:7">
+    <row r="71" customFormat="1" spans="7:7">
       <c r="G71" s="2"/>
     </row>
-    <row r="72" spans="7:7">
+    <row r="72" customFormat="1" spans="7:7">
       <c r="G72" s="2"/>
     </row>
   </sheetData>
@@ -4976,4 +5189,2396 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M72"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.71428571428571" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="26.2857142857143" style="1" customWidth="1"/>
+    <col min="4" max="4" width="105.714285714286" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.8571428571429" style="1" customWidth="1"/>
+    <col min="7" max="11" width="9" style="1"/>
+    <col min="12" max="12" width="14.7142857142857" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:13">
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="1">
+        <v>54</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="1">
+        <v>54</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="1">
+        <v>54</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="1">
+        <v>54</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:13">
+      <c r="A9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="1">
+        <v>54</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:13">
+      <c r="A10" s="1">
+        <v>101304</v>
+      </c>
+      <c r="B10" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2</v>
+      </c>
+      <c r="H10" s="1">
+        <v>54</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="1">
+        <v>10013</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:13">
+      <c r="A11" s="1">
+        <v>101303</v>
+      </c>
+      <c r="B11" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1">
+        <v>54</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="1">
+        <v>10013</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:13">
+      <c r="A12" s="1">
+        <v>101302</v>
+      </c>
+      <c r="B12" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>54</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" s="1">
+        <v>10013</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="14" customHeight="1" spans="1:13">
+      <c r="A13" s="1">
+        <v>101301</v>
+      </c>
+      <c r="B13" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13" s="1">
+        <v>54</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" s="1">
+        <v>10013</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:13">
+      <c r="A14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="1">
+        <v>54</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:13">
+      <c r="A15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="1">
+        <v>54</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:13">
+      <c r="A16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="1">
+        <v>54</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:13">
+      <c r="A17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:13">
+      <c r="A18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="1">
+        <v>54</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:13">
+      <c r="A19" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="1">
+        <v>54</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:13">
+      <c r="A20" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" s="1">
+        <v>54</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:13">
+      <c r="A21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1008</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="1">
+        <v>54</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:13">
+      <c r="A22" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:13">
+      <c r="A23" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" s="1">
+        <v>54</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:13">
+      <c r="A24" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1009</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="1">
+        <v>54</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:13">
+      <c r="A25" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="1">
+        <v>54</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:13">
+      <c r="A26" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="1">
+        <v>54</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1202</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:13">
+      <c r="A27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="1">
+        <v>54</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1202</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:13">
+      <c r="A28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" s="1">
+        <v>54</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:13">
+      <c r="A29" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="1">
+        <v>54</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1102</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:13">
+      <c r="A30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="1">
+        <v>54</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:13">
+      <c r="A31" s="1">
+        <v>100208</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1202</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="1">
+        <v>54</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1102</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:13">
+      <c r="A32" s="1">
+        <v>100207</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1202</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" s="1">
+        <v>54</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1102</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:13">
+      <c r="A33" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:13">
+      <c r="A34" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H34" s="1">
+        <v>54</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:13">
+      <c r="A35" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="1">
+        <v>54</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:13">
+      <c r="A36" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" s="1">
+        <v>54</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:13">
+      <c r="A37" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="1">
+        <v>54</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:13">
+      <c r="A38" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" s="1">
+        <v>54</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:13">
+      <c r="A39" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H39" s="1">
+        <v>54</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:13">
+      <c r="A40" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40" s="1">
+        <v>54</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:13">
+      <c r="A41" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H41" s="1">
+        <v>54</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:13">
+      <c r="A42" s="1">
+        <v>115708</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1157</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" s="1">
+        <v>54</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1157</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:13">
+      <c r="A43" s="1">
+        <v>115707</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1157</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="1">
+        <v>54</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1157</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:13">
+      <c r="A44" s="1">
+        <v>115706</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1157</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44" s="1">
+        <v>54</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1157</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:13">
+      <c r="A45" s="1">
+        <v>115705</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1157</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H45" s="1">
+        <v>54</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1157</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:13">
+      <c r="A46" s="1">
+        <v>115704</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1157</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" s="1">
+        <v>54</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K46" s="1">
+        <v>1157</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:13">
+      <c r="A47" s="1">
+        <v>115703</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1157</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H47" s="1">
+        <v>54</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K47" s="1">
+        <v>1157</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:13">
+      <c r="A48" s="1">
+        <v>115702</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1157</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="1">
+        <v>54</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1157</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:13">
+      <c r="A49" s="1">
+        <v>115701</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1157</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="1">
+        <v>54</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1157</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:13">
+      <c r="A50" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1505</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K50" s="1">
+        <v>1605</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:13">
+      <c r="A51" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1405</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K51" s="1">
+        <v>1505</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:13">
+      <c r="A52" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1305</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1405</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="1:13">
+      <c r="A53" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1205</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1305</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:13">
+      <c r="A54" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B54" s="1">
+        <v>1105</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" s="1">
+        <v>1205</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:13">
+      <c r="A55" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B55" s="1">
+        <v>1005</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H55" s="1">
+        <v>54</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K55" s="1">
+        <v>1105</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:13">
+      <c r="A56" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" spans="1:13">
+      <c r="A57" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H57" s="1">
+        <v>54</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" spans="1:13">
+      <c r="A58" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H58" s="1">
+        <v>54</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" spans="1:13">
+      <c r="A59" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H59" s="1">
+        <v>54</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" spans="1:13">
+      <c r="A60" s="1">
+        <v>1600101</v>
+      </c>
+      <c r="B60" s="1">
+        <v>16001</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H60" s="1">
+        <v>54</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K60" s="1">
+        <v>16001</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:13">
+      <c r="A61" s="1">
+        <v>1600102</v>
+      </c>
+      <c r="B61" s="1">
+        <v>16001</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H61" s="1">
+        <v>54</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K61" s="1">
+        <v>16001</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="7:7">
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="7:7">
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="7:7">
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="7:7">
+      <c r="G72" s="2"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1 A3:A59 A62:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>